--- a/meletes/pyrosvestires-rodou-2026/ΠΥΡΟΣΒΕΣΤΗΡΕΣ_ΡΟΔΟΥ_2026.xlsx
+++ b/meletes/pyrosvestires-rodou-2026/ΠΥΡΟΣΒΕΣΤΗΡΕΣ_ΡΟΔΟΥ_2026.xlsx
@@ -2034,18 +2034,18 @@
         <v>44</v>
       </c>
       <c r="F18" s="9">
-        <v>2.9</v>
+        <v>31.46</v>
       </c>
       <c r="G18" s="10">
         <v>1</v>
       </c>
       <c r="H18" s="9">
         <f>IF(OR(F18="",G18=""),"",F18*G18)</f>
-        <v>2.9</v>
+        <v>31.46</v>
       </c>
       <c r="I18" s="9">
         <f>IF(F18="","",F18*(1+'ΣΗΜΕΙΩΣΕΙΣ'!$B$2))</f>
-        <v>3.596</v>
+        <v>39.010400000000004</v>
       </c>
       <c r="J18" s="11" t="s">
         <v>45</v>
@@ -2130,18 +2130,18 @@
         <v>50</v>
       </c>
       <c r="F21" s="9">
-        <v>31.46</v>
+        <v>2.9</v>
       </c>
       <c r="G21" s="10">
         <v>3</v>
       </c>
       <c r="H21" s="9">
         <f>IF(OR(F21="",G21=""),"",F21*G21)</f>
-        <v>94.38</v>
+        <v>8.7</v>
       </c>
       <c r="I21" s="9">
         <f>IF(F21="","",F21*(1+'ΣΗΜΕΙΩΣΕΙΣ'!$B$2))</f>
-        <v>39.010400000000004</v>
+        <v>3.596</v>
       </c>
       <c r="J21" s="11" t="s">
         <v>51</v>
